--- a/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
@@ -86173,13 +86173,13 @@
         <v>5</v>
       </c>
       <c r="AX393" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY393" t="n">
         <v>11</v>
       </c>
       <c r="AZ393" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA393" t="n">
         <v>5</v>
@@ -86606,13 +86606,13 @@
         <v>5</v>
       </c>
       <c r="AW395" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX395" t="n">
         <v>7</v>
       </c>
       <c r="AY395" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ395" t="n">
         <v>12</v>
@@ -87914,13 +87914,13 @@
         <v>4</v>
       </c>
       <c r="AW401" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX401" t="n">
         <v>10</v>
       </c>
       <c r="AY401" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ401" t="n">
         <v>14</v>
@@ -88132,16 +88132,16 @@
         <v>5</v>
       </c>
       <c r="AW402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX402" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY402" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ402" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA402" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
@@ -87260,13 +87260,13 @@
         <v>4</v>
       </c>
       <c r="AW398" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX398" t="n">
         <v>12</v>
       </c>
       <c r="AY398" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ398" t="n">
         <v>16</v>
@@ -88353,13 +88353,13 @@
         <v>11</v>
       </c>
       <c r="AX403" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY403" t="n">
         <v>18</v>
       </c>
       <c r="AZ403" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA403" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
@@ -87475,7 +87475,7 @@
         <v>7</v>
       </c>
       <c r="AV399" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW399" t="n">
         <v>6</v>
@@ -87487,7 +87487,7 @@
         <v>13</v>
       </c>
       <c r="AZ399" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA399" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
@@ -87472,13 +87472,13 @@
         <v>2.75</v>
       </c>
       <c r="AU399" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW399" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX399" t="n">
         <v>6</v>
@@ -87487,7 +87487,7 @@
         <v>13</v>
       </c>
       <c r="AZ399" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA399" t="n">
         <v>7</v>
@@ -88135,13 +88135,13 @@
         <v>1</v>
       </c>
       <c r="AX402" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY402" t="n">
         <v>8</v>
       </c>
       <c r="AZ402" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA402" t="n">
         <v>2</v>
@@ -88562,22 +88562,22 @@
         <v>2.62</v>
       </c>
       <c r="AU404" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV404" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW404" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX404" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY404" t="n">
         <v>12</v>
       </c>
       <c r="AZ404" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA404" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP404"/>
+  <dimension ref="A1:BP407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2222,7 +2222,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.9399999999999999</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.71</v>
@@ -5271,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.13</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.28</v>
@@ -8544,7 +8544,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR37" t="n">
         <v>1.61</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.76</v>
@@ -11814,7 +11814,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR52" t="n">
         <v>1.49</v>
@@ -14212,7 +14212,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR63" t="n">
         <v>1.16</v>
@@ -14427,7 +14427,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.9399999999999999</v>
@@ -15735,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.22</v>
@@ -17915,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.9399999999999999</v>
@@ -18569,7 +18569,7 @@
         <v>0.33</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.9399999999999999</v>
@@ -19662,7 +19662,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR88" t="n">
         <v>0.97</v>
@@ -20313,7 +20313,7 @@
         <v>0.67</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.13</v>
@@ -21842,7 +21842,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR98" t="n">
         <v>1.5</v>
@@ -22275,7 +22275,7 @@
         <v>1.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.47</v>
@@ -23586,7 +23586,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR106" t="n">
         <v>1.46</v>
@@ -23801,7 +23801,7 @@
         <v>0.75</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.9399999999999999</v>
@@ -25763,7 +25763,7 @@
         <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.9399999999999999</v>
@@ -26202,7 +26202,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR118" t="n">
         <v>1.92</v>
@@ -26417,7 +26417,7 @@
         <v>1.6</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ119" t="n">
         <v>1</v>
@@ -26856,7 +26856,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR121" t="n">
         <v>1.34</v>
@@ -29254,7 +29254,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR132" t="n">
         <v>1.43</v>
@@ -30123,7 +30123,7 @@
         <v>0.6</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.13</v>
@@ -32088,7 +32088,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR145" t="n">
         <v>0.96</v>
@@ -32957,7 +32957,7 @@
         <v>1</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.8100000000000001</v>
@@ -33393,7 +33393,7 @@
         <v>1.2</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.47</v>
@@ -34486,7 +34486,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR156" t="n">
         <v>1.26</v>
@@ -34701,7 +34701,7 @@
         <v>0.5</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.6899999999999999</v>
@@ -36445,10 +36445,10 @@
         <v>1.33</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR165" t="n">
         <v>1.27</v>
@@ -37317,7 +37317,7 @@
         <v>1.57</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.75</v>
@@ -37971,7 +37971,7 @@
         <v>0.57</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.76</v>
@@ -38846,7 +38846,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR176" t="n">
         <v>1.71</v>
@@ -40154,7 +40154,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR182" t="n">
         <v>1.58</v>
@@ -41677,7 +41677,7 @@
         <v>1.63</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.88</v>
@@ -44075,10 +44075,10 @@
         <v>0.75</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR200" t="n">
         <v>1.31</v>
@@ -45822,7 +45822,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR208" t="n">
         <v>1.39</v>
@@ -46909,7 +46909,7 @@
         <v>1.44</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ213" t="n">
         <v>1.22</v>
@@ -48435,7 +48435,7 @@
         <v>0.44</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ220" t="n">
         <v>0.71</v>
@@ -50615,7 +50615,7 @@
         <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ230" t="n">
         <v>0.8100000000000001</v>
@@ -50836,7 +50836,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ231" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR231" t="n">
         <v>1.39</v>
@@ -51708,7 +51708,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR235" t="n">
         <v>1.12</v>
@@ -52359,7 +52359,7 @@
         <v>1.33</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ238" t="n">
         <v>1.06</v>
@@ -53667,7 +53667,7 @@
         <v>1</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ244" t="n">
         <v>0.9399999999999999</v>
@@ -55632,7 +55632,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ253" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR253" t="n">
         <v>1.67</v>
@@ -56283,7 +56283,7 @@
         <v>0.9</v>
       </c>
       <c r="AP256" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ256" t="n">
         <v>1.13</v>
@@ -58248,7 +58248,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ265" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR265" t="n">
         <v>1.29</v>
@@ -58899,7 +58899,7 @@
         <v>1.36</v>
       </c>
       <c r="AP268" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ268" t="n">
         <v>1.75</v>
@@ -59338,7 +59338,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ270" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR270" t="n">
         <v>1.37</v>
@@ -60643,7 +60643,7 @@
         <v>1.27</v>
       </c>
       <c r="AP276" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ276" t="n">
         <v>0.88</v>
@@ -61079,7 +61079,7 @@
         <v>1.2</v>
       </c>
       <c r="AP278" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ278" t="n">
         <v>1.22</v>
@@ -63262,7 +63262,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ288" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR288" t="n">
         <v>1.33</v>
@@ -64785,7 +64785,7 @@
         <v>1.38</v>
       </c>
       <c r="AP295" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ295" t="n">
         <v>1.06</v>
@@ -66311,7 +66311,7 @@
         <v>0.83</v>
       </c>
       <c r="AP302" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ302" t="n">
         <v>0.71</v>
@@ -66750,7 +66750,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ304" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR304" t="n">
         <v>1.14</v>
@@ -67186,7 +67186,7 @@
         <v>2.39</v>
       </c>
       <c r="AQ306" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR306" t="n">
         <v>1.5</v>
@@ -68055,7 +68055,7 @@
         <v>1.23</v>
       </c>
       <c r="AP310" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ310" t="n">
         <v>1.22</v>
@@ -71110,7 +71110,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ324" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR324" t="n">
         <v>1.99</v>
@@ -71543,7 +71543,7 @@
         <v>0.85</v>
       </c>
       <c r="AP326" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ326" t="n">
         <v>0.76</v>
@@ -73069,7 +73069,7 @@
         <v>1.29</v>
       </c>
       <c r="AP333" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ333" t="n">
         <v>1.06</v>
@@ -73726,7 +73726,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ336" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR336" t="n">
         <v>1.37</v>
@@ -74377,7 +74377,7 @@
         <v>0.62</v>
       </c>
       <c r="AP339" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ339" t="n">
         <v>0.6899999999999999</v>
@@ -75031,7 +75031,7 @@
         <v>0.79</v>
       </c>
       <c r="AP342" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ342" t="n">
         <v>0.76</v>
@@ -75688,7 +75688,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ345" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR345" t="n">
         <v>1.51</v>
@@ -76993,7 +76993,7 @@
         <v>1.64</v>
       </c>
       <c r="AP351" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ351" t="n">
         <v>1.71</v>
@@ -78522,7 +78522,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ358" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR358" t="n">
         <v>1.36</v>
@@ -79391,7 +79391,7 @@
         <v>1.33</v>
       </c>
       <c r="AP362" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ362" t="n">
         <v>1.22</v>
@@ -79609,7 +79609,7 @@
         <v>0.8</v>
       </c>
       <c r="AP363" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ363" t="n">
         <v>0.76</v>
@@ -81353,10 +81353,10 @@
         <v>0.87</v>
       </c>
       <c r="AP371" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ371" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AR371" t="n">
         <v>1.46</v>
@@ -82007,7 +82007,7 @@
         <v>1.31</v>
       </c>
       <c r="AP374" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ374" t="n">
         <v>1.22</v>
@@ -83315,7 +83315,7 @@
         <v>0.88</v>
       </c>
       <c r="AP380" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ380" t="n">
         <v>1</v>
@@ -85280,7 +85280,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ389" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR389" t="n">
         <v>1.66</v>
@@ -86806,7 +86806,7 @@
         <v>2</v>
       </c>
       <c r="AQ396" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR396" t="n">
         <v>1.62</v>
@@ -87675,7 +87675,7 @@
         <v>1.18</v>
       </c>
       <c r="AP400" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ400" t="n">
         <v>1.28</v>
@@ -88329,7 +88329,7 @@
         <v>1.56</v>
       </c>
       <c r="AP403" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ403" t="n">
         <v>1.47</v>
@@ -88626,6 +88626,660 @@
       </c>
       <c r="BP404" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="n">
+        <v>8216816</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>46084.69791666666</v>
+      </c>
+      <c r="F405" t="n">
+        <v>17</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Exeter City</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Burton Albion</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>0</v>
+      </c>
+      <c r="J405" t="n">
+        <v>0</v>
+      </c>
+      <c r="K405" t="n">
+        <v>0</v>
+      </c>
+      <c r="L405" t="n">
+        <v>1</v>
+      </c>
+      <c r="M405" t="n">
+        <v>1</v>
+      </c>
+      <c r="N405" t="n">
+        <v>2</v>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="Q405" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R405" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S405" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T405" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U405" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V405" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W405" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X405" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y405" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z405" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA405" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB405" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC405" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD405" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE405" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF405" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG405" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH405" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI405" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ405" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK405" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL405" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM405" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN405" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO405" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP405" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ405" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AR405" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS405" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT405" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU405" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV405" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW405" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX405" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY405" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ405" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA405" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB405" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC405" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD405" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE405" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF405" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG405" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH405" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI405" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ405" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BK405" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL405" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM405" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN405" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO405" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP405" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="n">
+        <v>8216912</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="n">
+        <v>46084.69791666666</v>
+      </c>
+      <c r="F406" t="n">
+        <v>26</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Wycombe Wanderers</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>0</v>
+      </c>
+      <c r="J406" t="n">
+        <v>0</v>
+      </c>
+      <c r="K406" t="n">
+        <v>0</v>
+      </c>
+      <c r="L406" t="n">
+        <v>0</v>
+      </c>
+      <c r="M406" t="n">
+        <v>1</v>
+      </c>
+      <c r="N406" t="n">
+        <v>1</v>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="Q406" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R406" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S406" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T406" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U406" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V406" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W406" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X406" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y406" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z406" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA406" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB406" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC406" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD406" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AE406" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF406" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AG406" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH406" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI406" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ406" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK406" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL406" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM406" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN406" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO406" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP406" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ406" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR406" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS406" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT406" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU406" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV406" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW406" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX406" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY406" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ406" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA406" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB406" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC406" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD406" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE406" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF406" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG406" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH406" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI406" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ406" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BK406" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL406" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM406" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN406" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO406" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP406" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="n">
+        <v>8216909</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>46084.69791666666</v>
+      </c>
+      <c r="F407" t="n">
+        <v>25</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Rotherham United</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Mansfield Town</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>0</v>
+      </c>
+      <c r="J407" t="n">
+        <v>0</v>
+      </c>
+      <c r="K407" t="n">
+        <v>0</v>
+      </c>
+      <c r="L407" t="n">
+        <v>0</v>
+      </c>
+      <c r="M407" t="n">
+        <v>0</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0</v>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q407" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R407" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S407" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T407" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U407" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V407" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W407" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X407" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y407" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z407" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA407" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB407" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC407" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD407" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE407" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF407" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG407" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH407" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI407" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ407" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK407" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL407" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM407" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN407" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO407" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AP407" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ407" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR407" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS407" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT407" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU407" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV407" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW407" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX407" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY407" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ407" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA407" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB407" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC407" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD407" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE407" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF407" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG407" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH407" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="BI407" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ407" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK407" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL407" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM407" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN407" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO407" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP407" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
@@ -88780,22 +88780,22 @@
         <v>2.73</v>
       </c>
       <c r="AU405" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV405" t="n">
         <v>4</v>
       </c>
       <c r="AW405" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX405" t="n">
         <v>9</v>
       </c>
-      <c r="AX405" t="n">
-        <v>7</v>
-      </c>
       <c r="AY405" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ405" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA405" t="n">
         <v>11</v>
@@ -89004,13 +89004,13 @@
         <v>8</v>
       </c>
       <c r="AW406" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX406" t="n">
         <v>11</v>
       </c>
       <c r="AY406" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ406" t="n">
         <v>19</v>

--- a/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
@@ -89876,13 +89876,13 @@
         <v>2</v>
       </c>
       <c r="AW410" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX410" t="n">
         <v>5</v>
       </c>
       <c r="AY410" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ410" t="n">
         <v>7</v>
@@ -90097,13 +90097,13 @@
         <v>6</v>
       </c>
       <c r="AX411" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY411" t="n">
         <v>12</v>
       </c>
       <c r="AZ411" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA411" t="n">
         <v>1</v>
@@ -90524,7 +90524,7 @@
         <v>3.37</v>
       </c>
       <c r="AU413" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV413" t="n">
         <v>9</v>
@@ -90536,7 +90536,7 @@
         <v>3</v>
       </c>
       <c r="AY413" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ413" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League One_20252026.xlsx
@@ -90097,13 +90097,13 @@
         <v>6</v>
       </c>
       <c r="AX411" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY411" t="n">
         <v>12</v>
       </c>
       <c r="AZ411" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA411" t="n">
         <v>1</v>
